--- a/artfynd/A 55060-2023 artfynd.xlsx
+++ b/artfynd/A 55060-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55060-2023 artfynd.xlsx
+++ b/artfynd/A 55060-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113273980</v>
+        <v>113274208</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566644</v>
+        <v>566652</v>
       </c>
       <c r="R2" t="n">
-        <v>6322812</v>
+        <v>6322795</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,11 +747,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113274447</v>
+        <v>113274436</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566652</v>
+        <v>566664</v>
       </c>
       <c r="R3" t="n">
-        <v>6322795</v>
+        <v>6322756</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113274208</v>
+        <v>113274447</v>
       </c>
       <c r="B4" t="n">
-        <v>90726</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -992,16 +972,11 @@
         <v>113273932</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1097,37 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113274436</v>
+        <v>113273980</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566664</v>
+        <v>566644</v>
       </c>
       <c r="R6" t="n">
-        <v>6322756</v>
+        <v>6322812</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1176,6 +1146,11 @@
           <t>2023-11-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1197,6 +1172,109 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113274465</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hjortnäset, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566693</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6322772</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Långemåla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55060-2023 artfynd.xlsx
+++ b/artfynd/A 55060-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113274208</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113274436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113274447</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273932</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113273980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,8 +1305,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113274465</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>